--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-practitioner.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Practitioner</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Practitioner|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -368,7 +368,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -542,7 +542,7 @@
     <t>Practitioner.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {http://jpfhir.jp/fhir/core/StructureDefinition/JP_HumanName}
+    <t xml:space="preserve">HumanName {http://jpfhir.jp/fhir/core/StructureDefinition/JP_HumanName|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1302,7 +1302,7 @@
     <t>特定の資格開業医はサービスを提供する必要があります。 / Specific qualification the practitioner has to provide a service.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-2.7-0360</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-2.7-0360|0360</t>
   </si>
   <si>
     <t>./Qualifications.Value</t>
@@ -1333,7 +1333,7 @@
     <t>Practitioner.qualification.issuer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1445,7 +1445,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1583,7 +1583,7 @@
     <t>Practitioner.qualification.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1619,7 +1619,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicalLicenseCertificate_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicalLicenseCertificate_VS|1.1.0</t>
   </si>
   <si>
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.period</t>
@@ -2040,7 +2040,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="60.1640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="68.15625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2055,7 +2055,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.0859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-practitioner.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Practitioner|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Practitioner</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -368,7 +368,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -542,7 +542,7 @@
     <t>Practitioner.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {http://jpfhir.jp/fhir/core/StructureDefinition/JP_HumanName|1.3.0-dev}
+    <t xml:space="preserve">HumanName {http://jpfhir.jp/fhir/core/StructureDefinition/JP_HumanName}
 </t>
   </si>
   <si>
@@ -1302,7 +1302,7 @@
     <t>特定の資格開業医はサービスを提供する必要があります。 / Specific qualification the practitioner has to provide a service.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-2.7-0360|0360</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-2.7-0360</t>
   </si>
   <si>
     <t>./Qualifications.Value</t>
@@ -1333,7 +1333,7 @@
     <t>Practitioner.qualification.issuer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1445,7 +1445,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1583,7 +1583,7 @@
     <t>Practitioner.qualification.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -1619,7 +1619,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicalLicenseCertificate_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicalLicenseCertificate_VS</t>
   </si>
   <si>
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.period</t>
@@ -2040,7 +2040,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.15625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="60.1640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2055,7 +2055,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.6171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.0859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
